--- a/output/pdf_financials_xlsx/EOG.xlsx
+++ b/output/pdf_financials_xlsx/EOG.xlsx
@@ -1312,7 +1312,7 @@
         <v>-0.560729</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-5.685061</v>
@@ -1632,7 +1632,7 @@
         <v>-0.560729</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-5.685061</v>
@@ -1819,7 +1819,7 @@
         <v>-0.560729</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-5.685061</v>
@@ -2139,7 +2139,7 @@
         <v>-0.560729</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.685061</v>
@@ -2265,7 +2265,7 @@
         <v>-0.560729</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.684664</v>
@@ -2409,7 +2409,7 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -6312,22 +6312,22 @@
         <v>0</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-1.117859</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-1.198097</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-1.309727</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-1.458709</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-1.568469</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-1.527171</v>
       </c>
     </row>
     <row r="92">
@@ -10956,7 +10956,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -69863,10 +69867,10 @@
         </is>
       </c>
       <c r="H583" s="5" t="n">
-        <v>0.456573</v>
+        <v>-0.456573</v>
       </c>
       <c r="I583" s="5" t="n">
-        <v>5.685061</v>
+        <v>-5.685061</v>
       </c>
       <c r="J583" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EOG.xlsx
+++ b/output/pdf_financials_xlsx/EOG.xlsx
@@ -958,22 +958,22 @@
         <v>3.218148</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.179666</v>
+        <v>5.444966</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.107496</v>
+        <v>3.144667</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>4.060879</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>9.690134</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>12.774784</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>20.451725</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>3.531382</v>
@@ -1019,22 +1019,22 @@
         <v>-3.1517</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5.444966</v>
+        <v>0.179666</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-4.541295</v>
+        <v>-2.578466</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.01582</v>
+        <v>-4.045059</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.33362</v>
+        <v>-8.356514000000001</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16.948417</v>
+        <v>4.173633</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.378194</v>
+        <v>-20.073531</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-3.484285</v>
@@ -1059,58 +1059,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.026358</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002927</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.012473</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.063858</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.06644799999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.029625</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.011801</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.01582</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.08562</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.28911</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.378194</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.047097</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003556</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.06657100000000001</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001708</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.092074</v>
       </c>
     </row>
     <row r="13">
@@ -2130,34 +2130,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.10218</v>
+        <v>-0.128538</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.086644</v>
+        <v>-0.08674</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.560729</v>
+        <v>-0.563656</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.456573</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.685061</v>
+        <v>-5.697534</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.984202</v>
+        <v>-4.04806</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.179666</v>
+        <v>0.113218</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.179666</v>
+        <v>0.150041</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.107496</v>
+        <v>-5.119297</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.556586</v>
+        <v>-3.572406</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2170,22 +2170,22 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-20.073531</v>
+        <v>-20.451725</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.679807</v>
+        <v>-3.726904</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.557324</v>
+        <v>-6.56088</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-36.554754</v>
+        <v>-36.621325</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-21.247659</v>
+        <v>-21.245951</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-2.236251</v>
+        <v>-2.144177</v>
       </c>
     </row>
     <row r="28">
@@ -2256,34 +2256,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.10218</v>
+        <v>-0.128538</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.086644</v>
+        <v>-0.08674</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.560729</v>
+        <v>-0.563656</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.456573</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.684664</v>
+        <v>-5.697137</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.981805</v>
+        <v>-4.045663</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.18237</v>
+        <v>0.115922</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.183141</v>
+        <v>0.153516</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.101025</v>
+        <v>-5.112826</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.555485</v>
+        <v>-3.571305</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2296,22 +2296,22 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-20.073531</v>
+        <v>-20.451725</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.655603</v>
+        <v>-3.7027</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.557324</v>
+        <v>-6.56088</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-36.554754</v>
+        <v>-36.621325</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-21.247659</v>
+        <v>-21.245951</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-2.236251</v>
+        <v>-2.144177</v>
       </c>
     </row>
     <row r="30">
@@ -2351,16 +2351,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>274.4552130989646</v>
+        <v>174.4552130989646</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.256053018224125</v>
+        <v>2.729351893599439</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-900.9212276205799</v>
+        <v>-903.0054697889972</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-22474.62073324905</v>
+        <v>-22574.62073324905</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-5307.733861457347</v>
+        <v>-5407.733861457347</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-7761.859566426736</v>
+        <v>-7861.859566426736</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-184401.6872890889</v>
+        <v>-184501.6872890889</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-54910.92818194108</v>
+        <v>-55010.92818194108</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-1244008.138173302</v>
+        <v>-1243908.138173302</v>
       </c>
       <c r="S30" s="1" t="inlineStr">
         <is>
@@ -2550,10 +2550,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>1.625905</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.501801</v>
@@ -2676,10 +2674,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>1.625905</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.501801</v>
@@ -25028,7 +25024,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -46484,7 +46480,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -47966,7 +47962,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -53362,7 +53358,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -54628,7 +54624,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -55240,7 +55236,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -71018,7 +71014,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -71876,7 +71872,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E602" s="5" t="n">

--- a/output/pdf_financials_xlsx/EOG.xlsx
+++ b/output/pdf_financials_xlsx/EOG.xlsx
@@ -6754,10 +6754,10 @@
         <v>0.179666</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-5.107496</v>
+        <v>-3.77415</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-3.556586</v>
+        <v>-4.045059</v>
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
@@ -6773,16 +6773,16 @@
         <v>-20.073531</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>-3.679807</v>
+        <v>-3.484285</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>-6.557324</v>
+        <v>-5.252387</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>-36.554754</v>
+        <v>-36.634958</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>-21.247659</v>
+        <v>-21.137899</v>
       </c>
       <c r="S99" s="3" t="n">
         <v>-2.236251</v>
@@ -8109,13 +8109,13 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.0297</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.787143</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.338257</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -29364,7 +29364,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -33714,7 +33718,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -35156,7 +35164,11 @@
           <t>Net proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36314,7 +36326,11 @@
           <t>Net proceeds from Brokered Private Placement</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -36942,7 +36958,11 @@
           <t>Net loss from continued operations $</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -37878,7 +37898,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
